--- a/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27016"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/alireza_mohammadi_undp_org/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E21EDA7-8082-4A95-BE2A-C411FA3966C4}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90184C2C-EA5A-4A38-8B60-9CA2D50B4CF8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="84">
   <si>
     <t>Project ID</t>
   </si>
@@ -165,7 +168,7 @@
 of ministry of power ( MoP</t>
   </si>
   <si>
-    <t>Other Energy Services</t>
+    <t>GHG Emissions Reduction</t>
   </si>
   <si>
     <t>tCO2 saved</t>
@@ -180,6 +183,9 @@
   <si>
     <t xml:space="preserve">
 0.375 </t>
+  </si>
+  <si>
+    <t>Other Energy Services</t>
   </si>
   <si>
     <t>GEF: 4,000,000</t>
@@ -455,7 +461,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -544,39 +550,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -593,16 +570,20 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -617,7 +598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -829,9 +810,6 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -853,6 +831,54 @@
     <xf numFmtId="3" fontId="8" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -865,9 +891,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -888,60 +911,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="12" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1271,16 +1240,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" s="77" customFormat="1" ht="45.75">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="83" t="s">
+      <c r="D1" s="96" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="82" t="s">
@@ -1298,34 +1267,34 @@
       <c r="I1" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="84" t="s">
+      <c r="J1" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="84" t="s">
+      <c r="K1" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="84" t="s">
+      <c r="L1" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="84" t="s">
+      <c r="M1" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="85" t="s">
+      <c r="N1" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="85" t="s">
+      <c r="O1" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="85" t="s">
+      <c r="P1" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="85" t="s">
+      <c r="Q1" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="85" t="s">
+      <c r="R1" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="85" t="s">
+      <c r="S1" s="84" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="5"/>
@@ -1347,19 +1316,19 @@
       <c r="AJ1" s="5"/>
     </row>
     <row r="2" spans="1:36" s="78" customFormat="1" ht="60" customHeight="1">
-      <c r="A2" s="108">
+      <c r="A2" s="99">
         <v>63735</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="108">
+      <c r="D2" s="92">
         <v>4000000</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="90" t="s">
         <v>21</v>
       </c>
       <c r="F2" s="79" t="s">
@@ -1415,17 +1384,17 @@
       <c r="AJ2" s="8"/>
     </row>
     <row r="3" spans="1:36" s="78" customFormat="1" ht="69.75" customHeight="1">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="113"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="105" t="s">
+      <c r="A3" s="93"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="90" t="s">
         <v>30</v>
       </c>
       <c r="F3" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="86">
+      <c r="G3" s="85">
         <v>0</v>
       </c>
       <c r="H3" s="79">
@@ -1467,11 +1436,11 @@
       <c r="AJ3" s="8"/>
     </row>
     <row r="4" spans="1:36" s="78" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="104"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="105" t="s">
+      <c r="A4" s="93"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="90" t="s">
         <v>30</v>
       </c>
       <c r="F4" s="79" t="s">
@@ -1517,20 +1486,20 @@
       <c r="AJ4" s="8"/>
     </row>
     <row r="5" spans="1:36" s="78" customFormat="1" ht="56.25" customHeight="1">
-      <c r="A5" s="115"/>
-      <c r="B5" s="103"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="106" t="s">
+      <c r="A5" s="93"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="88">
+      <c r="G5" s="87">
         <v>0</v>
       </c>
-      <c r="H5" s="89">
+      <c r="H5" s="88">
         <v>20000</v>
       </c>
       <c r="I5" s="68" t="s">
@@ -1569,20 +1538,20 @@
       <c r="AJ5" s="8"/>
     </row>
     <row r="6" spans="1:36" s="78" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A6" s="117"/>
-      <c r="B6" s="118"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="107" t="s">
+      <c r="A6" s="94"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="87" t="s">
+      <c r="F6" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="87">
         <v>0</v>
       </c>
-      <c r="H6" s="90">
+      <c r="H6" s="89">
         <v>146167</v>
       </c>
       <c r="I6" s="68" t="s">
@@ -1635,7 +1604,6 @@
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
       <c r="E8" s="70"/>
       <c r="F8" s="70"/>
       <c r="G8" s="70"/>
@@ -1845,16 +1813,16 @@
       <c r="AJ1" s="72"/>
     </row>
     <row r="2" spans="1:36" s="54" customFormat="1" ht="60" customHeight="1">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="96">
+      <c r="D2" s="110">
         <v>4000000</v>
       </c>
       <c r="E2" s="59" t="s">
@@ -1870,11 +1838,11 @@
       <c r="I2" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="95" t="s">
+      <c r="J2" s="105" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="62"/>
-      <c r="L2" s="95" t="s">
+      <c r="L2" s="105" t="s">
         <v>25</v>
       </c>
       <c r="M2" s="62"/>
@@ -1911,10 +1879,10 @@
       <c r="AJ2" s="69"/>
     </row>
     <row r="3" spans="1:36" s="54" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A3" s="96"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="96"/>
+      <c r="A3" s="110"/>
+      <c r="B3" s="111"/>
+      <c r="C3" s="112"/>
+      <c r="D3" s="110"/>
       <c r="E3" s="59" t="s">
         <v>30</v>
       </c>
@@ -1930,9 +1898,9 @@
       <c r="I3" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="95"/>
+      <c r="J3" s="105"/>
       <c r="K3" s="62"/>
-      <c r="L3" s="95"/>
+      <c r="L3" s="105"/>
       <c r="M3" s="62"/>
       <c r="N3" s="69"/>
       <c r="O3" s="69" t="s">
@@ -1963,10 +1931,10 @@
       <c r="AJ3" s="69"/>
     </row>
     <row r="4" spans="1:36" s="54" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A4" s="96"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="96"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="112"/>
+      <c r="D4" s="110"/>
       <c r="E4" s="59" t="s">
         <v>30</v>
       </c>
@@ -1980,9 +1948,9 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="64"/>
-      <c r="J4" s="95"/>
+      <c r="J4" s="105"/>
       <c r="K4" s="62"/>
-      <c r="L4" s="95"/>
+      <c r="L4" s="105"/>
       <c r="M4" s="65"/>
       <c r="N4" s="69"/>
       <c r="O4" s="69" t="s">
@@ -2013,10 +1981,10 @@
       <c r="AJ4" s="69"/>
     </row>
     <row r="5" spans="1:36" s="54" customFormat="1" ht="39" customHeight="1">
-      <c r="A5" s="96"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="96"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="110"/>
       <c r="E5" s="66" t="s">
         <v>35</v>
       </c>
@@ -2032,9 +2000,9 @@
       <c r="I5" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="95"/>
+      <c r="J5" s="105"/>
       <c r="K5" s="62"/>
-      <c r="L5" s="95"/>
+      <c r="L5" s="105"/>
       <c r="M5" s="65"/>
       <c r="N5" s="69"/>
       <c r="O5" s="69" t="s">
@@ -2065,12 +2033,12 @@
       <c r="AJ5" s="69"/>
     </row>
     <row r="6" spans="1:36" s="54" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A6" s="96"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="96"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="110"/>
       <c r="E6" s="67" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" s="66" t="s">
         <v>39</v>
@@ -2084,9 +2052,9 @@
       <c r="I6" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="95"/>
+      <c r="J6" s="105"/>
       <c r="K6" s="62"/>
-      <c r="L6" s="95"/>
+      <c r="L6" s="105"/>
       <c r="M6" s="65"/>
       <c r="N6" s="69"/>
       <c r="O6" s="69" t="s">
@@ -2215,62 +2183,62 @@
       <c r="H15" s="21"/>
     </row>
     <row r="16" spans="1:36">
-      <c r="A16" s="91"/>
-      <c r="B16" s="92"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="94"/>
+      <c r="A16" s="106"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="109"/>
       <c r="F16" s="17"/>
       <c r="G16" s="16"/>
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="91"/>
-      <c r="B17" s="92"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="94"/>
+      <c r="A17" s="106"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="109"/>
       <c r="F17" s="17"/>
       <c r="G17" s="16"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="91"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="109"/>
       <c r="G18" s="25"/>
       <c r="I18" s="19"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="94"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="109"/>
       <c r="G19" s="16"/>
       <c r="H19"/>
       <c r="I19" s="19"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="94"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="109"/>
       <c r="F20" s="24"/>
       <c r="G20" s="25"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="94"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
       <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:9">
@@ -2469,7 +2437,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" s="46" t="s">
         <v>21</v>
@@ -2481,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I3" s="48" t="s">
         <v>23</v>
@@ -2502,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I4" s="49" t="s">
         <v>32</v>
@@ -2523,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="51"/>
     </row>
@@ -2542,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="52" t="s">
         <v>37</v>
@@ -2557,13 +2525,13 @@
         <v>30</v>
       </c>
       <c r="F7" s="52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="51">
         <v>0</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I7" s="52" t="s">
         <v>40</v>
@@ -2679,62 +2647,62 @@
       <c r="H17" s="21"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="91"/>
-      <c r="B18" s="92"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94"/>
+      <c r="A18" s="106"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="109"/>
       <c r="F18" s="17"/>
       <c r="G18" s="16"/>
       <c r="H18" s="18"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="91"/>
-      <c r="B19" s="92"/>
-      <c r="C19" s="93"/>
-      <c r="D19" s="94"/>
+      <c r="A19" s="106"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="109"/>
       <c r="F19" s="17"/>
       <c r="G19" s="16"/>
       <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="94"/>
+      <c r="A20" s="106"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="109"/>
       <c r="G20" s="25"/>
       <c r="I20" s="19"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="91"/>
-      <c r="B21" s="92"/>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
       <c r="G21" s="16"/>
       <c r="H21"/>
       <c r="I21" s="19"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="94"/>
+      <c r="A22" s="106"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="109"/>
       <c r="F22" s="24"/>
       <c r="G22" s="25"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="94"/>
+      <c r="A23" s="106"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="94"/>
+      <c r="A24" s="106"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="109"/>
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:9">
@@ -2854,160 +2822,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="99" t="s">
-        <v>52</v>
+      <c r="A2" s="113" t="s">
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="99"/>
+      <c r="A3" s="113"/>
       <c r="B3" t="s">
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="99"/>
+      <c r="A4" s="113"/>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="100" t="s">
-        <v>58</v>
+      <c r="A5" s="114" t="s">
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="100"/>
+      <c r="A6" s="114"/>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="100"/>
+      <c r="A7" s="114"/>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="100"/>
+      <c r="A8" s="114"/>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="100"/>
+      <c r="A9" s="114"/>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="101" t="s">
-        <v>68</v>
+      <c r="A10" s="115" t="s">
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="101"/>
+      <c r="A11" s="115"/>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="102" t="s">
-        <v>73</v>
+      <c r="A12" s="116" t="s">
+        <v>74</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="102"/>
+      <c r="A13" s="116"/>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="102"/>
+      <c r="A14" s="116"/>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3022,26 +2990,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3290,14 +3238,34 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532F36DD-ACCD-4FB5-BC3D-775EBA27E19D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532F36DD-ACCD-4FB5-BC3D-775EBA27E19D}"/>
 </file>
--- a/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27424"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/alireza_mohammadi_undp_org/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{615068E2-4B8F-42A1-A819-6304AA50D64E}"/>
+  <xr:revisionPtr revIDLastSave="232" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D7B744-0346-4850-B12B-F9DC167D2EAF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="95">
   <si>
     <t>Project ID</t>
   </si>
@@ -124,7 +124,7 @@
     <t>GEF</t>
   </si>
   <si>
-    <t>Non-VF</t>
+    <t>VF</t>
   </si>
   <si>
     <t>Accelerating just energy transition</t>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>0063735</t>
-  </si>
-  <si>
-    <t>VF</t>
   </si>
   <si>
     <t>Incentives and Support</t>
@@ -928,6 +925,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -952,7 +950,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1359,7 +1356,7 @@
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="60.75">
       <c r="A2" s="97">
-        <v>63735</v>
+        <v>4018</v>
       </c>
       <c r="B2" s="97" t="s">
         <v>21</v>
@@ -1528,7 +1525,7 @@
       <c r="B6" s="92"/>
       <c r="C6" s="93"/>
       <c r="D6" s="94"/>
-      <c r="E6" s="118" t="s">
+      <c r="E6" s="110" t="s">
         <v>39</v>
       </c>
       <c r="F6" s="95" t="s">
@@ -1802,16 +1799,16 @@
       <c r="AJ1" s="69"/>
     </row>
     <row r="2" spans="1:36" s="51" customFormat="1" ht="60" customHeight="1">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="115">
+      <c r="D2" s="116">
         <v>4000000</v>
       </c>
       <c r="E2" s="56" t="s">
@@ -1827,12 +1824,12 @@
       <c r="I2" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="110" t="s">
+      <c r="J2" s="111" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="59"/>
-      <c r="L2" s="110" t="s">
-        <v>45</v>
+      <c r="L2" s="111" t="s">
+        <v>26</v>
       </c>
       <c r="M2" s="59"/>
       <c r="N2" s="66"/>
@@ -1844,7 +1841,7 @@
       </c>
       <c r="Q2" s="66"/>
       <c r="R2" s="66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S2" s="66" t="s">
         <v>28</v>
@@ -1868,10 +1865,10 @@
       <c r="AJ2" s="66"/>
     </row>
     <row r="3" spans="1:36" s="51" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A3" s="115"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="115"/>
+      <c r="A3" s="116"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="56" t="s">
         <v>31</v>
       </c>
@@ -1882,21 +1879,21 @@
         <v>0</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I3" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="110"/>
+      <c r="J3" s="111"/>
       <c r="K3" s="59"/>
-      <c r="L3" s="110"/>
+      <c r="L3" s="111"/>
       <c r="M3" s="59"/>
       <c r="N3" s="66"/>
       <c r="O3" s="66" t="s">
         <v>27</v>
       </c>
       <c r="P3" s="66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="66"/>
       <c r="R3" s="66"/>
@@ -1920,10 +1917,10 @@
       <c r="AJ3" s="66"/>
     </row>
     <row r="4" spans="1:36" s="51" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="117"/>
-      <c r="D4" s="115"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="117"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="116"/>
       <c r="E4" s="56" t="s">
         <v>31</v>
       </c>
@@ -1937,16 +1934,16 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="61"/>
-      <c r="J4" s="110"/>
+      <c r="J4" s="111"/>
       <c r="K4" s="59"/>
-      <c r="L4" s="110"/>
+      <c r="L4" s="111"/>
       <c r="M4" s="62"/>
       <c r="N4" s="66"/>
       <c r="O4" s="66" t="s">
         <v>27</v>
       </c>
       <c r="P4" s="66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q4" s="66"/>
       <c r="R4" s="66"/>
@@ -1970,12 +1967,12 @@
       <c r="AJ4" s="66"/>
     </row>
     <row r="5" spans="1:36" s="51" customFormat="1" ht="39" customHeight="1">
-      <c r="A5" s="115"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="115"/>
+      <c r="A5" s="116"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="116"/>
       <c r="E5" s="63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="64" t="s">
         <v>37</v>
@@ -1989,16 +1986,16 @@
       <c r="I5" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="110"/>
+      <c r="J5" s="111"/>
       <c r="K5" s="59"/>
-      <c r="L5" s="110"/>
+      <c r="L5" s="111"/>
       <c r="M5" s="62"/>
       <c r="N5" s="66"/>
       <c r="O5" s="66" t="s">
         <v>27</v>
       </c>
       <c r="P5" s="66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q5" s="66"/>
       <c r="R5" s="66"/>
@@ -2022,12 +2019,12 @@
       <c r="AJ5" s="66"/>
     </row>
     <row r="6" spans="1:36" s="51" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A6" s="115"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="115"/>
+      <c r="A6" s="116"/>
+      <c r="B6" s="117"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="116"/>
       <c r="E6" s="64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" s="63" t="s">
         <v>40</v>
@@ -2041,16 +2038,16 @@
       <c r="I6" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="110"/>
+      <c r="J6" s="111"/>
       <c r="K6" s="59"/>
-      <c r="L6" s="110"/>
+      <c r="L6" s="111"/>
       <c r="M6" s="62"/>
       <c r="N6" s="66"/>
       <c r="O6" s="66" t="s">
         <v>27</v>
       </c>
       <c r="P6" s="66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="66"/>
       <c r="R6" s="66"/>
@@ -2172,62 +2169,62 @@
       <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:36">
-      <c r="A16" s="111"/>
-      <c r="B16" s="112"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="114"/>
+      <c r="A16" s="112"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="115"/>
       <c r="F16" s="14"/>
       <c r="G16" s="13"/>
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="111"/>
-      <c r="B17" s="112"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="114"/>
+      <c r="A17" s="112"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
       <c r="F17" s="14"/>
       <c r="G17" s="13"/>
       <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="111"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="114"/>
+      <c r="A18" s="112"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="115"/>
       <c r="G18" s="22"/>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="111"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
+      <c r="A19" s="112"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="115"/>
       <c r="G19" s="13"/>
       <c r="H19"/>
       <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="111"/>
-      <c r="B20" s="112"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="114"/>
+      <c r="A20" s="112"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="115"/>
       <c r="F20" s="21"/>
       <c r="G20" s="22"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="111"/>
-      <c r="B21" s="112"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="114"/>
+      <c r="A21" s="112"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="115"/>
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="111"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="114"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="115"/>
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:9">
@@ -2426,7 +2423,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>19</v>
@@ -2438,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I3" s="45" t="s">
         <v>24</v>
@@ -2459,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I4" s="46" t="s">
         <v>33</v>
@@ -2480,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I5" s="48"/>
     </row>
@@ -2490,7 +2487,7 @@
       <c r="C6" s="11"/>
       <c r="D6" s="12"/>
       <c r="E6" s="49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>37</v>
@@ -2499,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I6" s="49" t="s">
         <v>38</v>
@@ -2514,13 +2511,13 @@
         <v>31</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="48">
         <v>0</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I7" s="49" t="s">
         <v>41</v>
@@ -2636,62 +2633,62 @@
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="111"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="114"/>
+      <c r="A18" s="112"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="115"/>
       <c r="F18" s="14"/>
       <c r="G18" s="13"/>
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="111"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
+      <c r="A19" s="112"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="115"/>
       <c r="F19" s="14"/>
       <c r="G19" s="13"/>
       <c r="H19" s="15"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="111"/>
-      <c r="B20" s="112"/>
-      <c r="C20" s="113"/>
-      <c r="D20" s="114"/>
+      <c r="A20" s="112"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="115"/>
       <c r="G20" s="22"/>
       <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="111"/>
-      <c r="B21" s="112"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="114"/>
+      <c r="A21" s="112"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="115"/>
       <c r="G21" s="13"/>
       <c r="H21"/>
       <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="111"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="114"/>
+      <c r="A22" s="112"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="115"/>
       <c r="F22" s="21"/>
       <c r="G22" s="22"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="111"/>
-      <c r="B23" s="112"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="114"/>
+      <c r="A23" s="112"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="115"/>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="111"/>
-      <c r="B24" s="112"/>
-      <c r="C24" s="113"/>
-      <c r="D24" s="114"/>
+      <c r="A24" s="112"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="115"/>
       <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:9">
@@ -2818,10 +2815,10 @@
     </row>
     <row r="2" spans="1:2" ht="30.75">
       <c r="A2" s="119" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="103" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" s="103" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2829,111 +2826,111 @@
         <v>31</v>
       </c>
       <c r="B3" s="103" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
       <c r="A4" s="119" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="103" t="s">
         <v>61</v>
-      </c>
-      <c r="B4" s="103" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="119" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="103" t="s">
         <v>63</v>
-      </c>
-      <c r="B5" s="103" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45.75">
       <c r="A6" s="119" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="103" t="s">
         <v>65</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
       <c r="A7" s="119" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="103" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="103" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30.75">
       <c r="A8" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="103" t="s">
         <v>69</v>
-      </c>
-      <c r="B8" s="103" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30.75">
       <c r="A9" s="119" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="103" t="s">
         <v>71</v>
-      </c>
-      <c r="B9" s="103" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
       <c r="A10" s="119" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="120" t="s">
         <v>73</v>
-      </c>
-      <c r="B10" s="120" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="119" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="120" t="s">
         <v>75</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30.75">
       <c r="A12" s="119" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="103" t="s">
         <v>77</v>
-      </c>
-      <c r="B12" s="103" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="120" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="120" t="s">
         <v>80</v>
-      </c>
-      <c r="B14" s="120" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="119" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="120" t="s">
         <v>82</v>
-      </c>
-      <c r="B15" s="120" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="119" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="120" t="s">
         <v>84</v>
-      </c>
-      <c r="B16" s="120" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2941,31 +2938,31 @@
         <v>36</v>
       </c>
       <c r="B17" s="103" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="120" t="s">
         <v>87</v>
-      </c>
-      <c r="B18" s="120" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
       <c r="A19" s="119" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="120" t="s">
         <v>89</v>
-      </c>
-      <c r="B19" s="120" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="119" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="120" t="s">
         <v>91</v>
-      </c>
-      <c r="B20" s="120" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
@@ -2973,15 +2970,15 @@
         <v>19</v>
       </c>
       <c r="B21" s="121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="119" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="120" t="s">
         <v>94</v>
-      </c>
-      <c r="B22" s="120" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2999,19 +2996,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3036,6 +3022,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3115,6 +3102,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3258,14 +3250,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BBFE1BD-9BE7-450B-B956-AF3B3ABCBDB9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532F36DD-ACCD-4FB5-BC3D-775EBA27E19D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27424"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp-my.sharepoint.com/personal/alireza_mohammadi_undp_org/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="232" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70D7B744-0346-4850-B12B-F9DC167D2EAF}"/>
+  <xr:revisionPtr revIDLastSave="351" documentId="8_{696420EF-8F51-4940-B3FE-F0CDA19E40C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02C7B3EF-E6EC-403B-B70C-FDCB381E1304}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="107">
   <si>
     <t>Project ID</t>
   </si>
@@ -181,6 +181,50 @@
 municipality and 6 other buildings)</t>
   </si>
   <si>
+    <t>(Agrovoltaics)Project for Developing Wetlands Conservation System in Lake Urmia and Other Wetlands Basin Communities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://open.undp.org/projects/00128285
+UNDP Transparency Portal
+ </t>
+  </si>
+  <si>
+    <t>Implementation of Energy Efficiency and Renewable Energy (Solar) in targeted farms</t>
+  </si>
+  <si>
+    <t>Government of Japan</t>
+  </si>
+  <si>
+    <t>non-VF</t>
+  </si>
+  <si>
+    <t>Renewable Energy</t>
+  </si>
+  <si>
+    <t>Water Stress in Chabahar</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00146138</t>
+  </si>
+  <si>
+    <t>Water Services</t>
+  </si>
+  <si>
+    <t>No. People have accerss to drinking water</t>
+  </si>
+  <si>
+    <t>This innitiative seeks to provide sustainable and clean water and energy solutions</t>
+  </si>
+  <si>
+    <t>Solar and Water Deasalineation</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t>Category</t>
   </si>
   <si>
@@ -195,9 +239,6 @@
   <si>
     <t xml:space="preserve">
 0.375 </t>
-  </si>
-  <si>
-    <t>Renewable Energy</t>
   </si>
   <si>
     <t>Capacity Training</t>
@@ -264,9 +305,6 @@
   </si>
   <si>
     <t>Number of people who gain access to health care facilities (direct access to electricity and heating systems for clinics, hospitals, health centers etc.) </t>
-  </si>
-  <si>
-    <t>Water Services</t>
   </si>
   <si>
     <t>Number of people who gain access to water services (powering water pumps, water distributions, waste management, etc.).  </t>
@@ -351,10 +389,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -438,6 +478,27 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="-Apple-System"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -477,7 +538,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -567,17 +628,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -622,11 +672,13 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <right style="thin">
         <color rgb="FF000000"/>
-      </bottom>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -634,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -819,9 +871,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -849,9 +898,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -870,34 +916,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -915,7 +940,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -925,7 +950,106 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -949,6 +1073,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1270,13 +1416,14 @@
     <col min="1" max="1" width="15.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="45.140625" style="2" customWidth="1"/>
     <col min="3" max="3" width="41.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="150" customWidth="1"/>
     <col min="5" max="5" width="43.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="35" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="20.140625" style="1" customWidth="1"/>
     <col min="9" max="9" width="65.140625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" style="2"/>
+    <col min="10" max="10" width="19.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="2"/>
     <col min="12" max="12" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1299,312 +1446,443 @@
       <c r="C1" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="104" t="s">
+      <c r="L1" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="105" t="s">
+      <c r="M1" s="96" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="104" t="s">
+      <c r="N1" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="104" t="s">
+      <c r="O1" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="105" t="s">
+      <c r="P1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="105" t="s">
+      <c r="Q1" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="106" t="s">
+      <c r="R1" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="107" t="s">
+      <c r="S1" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="106" t="s">
+      <c r="T1" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="107" t="s">
+      <c r="U1" s="98" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="60.75">
-      <c r="A2" s="97">
+      <c r="A2" s="89">
         <v>4018</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="99">
+      <c r="D2" s="144">
         <v>4000000</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="78">
+      <c r="G2" s="77">
         <v>0</v>
       </c>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="80" t="s">
+      <c r="J2" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="78"/>
-      <c r="L2" s="108" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="101"/>
-      <c r="N2" s="109" t="s">
+      <c r="M2" s="92"/>
+      <c r="N2" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="101" t="s">
+      <c r="O2" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101" t="s">
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="101" t="s">
+      <c r="R2" s="92" t="s">
         <v>28</v>
       </c>
       <c r="S2" s="66"/>
-      <c r="T2" s="101" t="s">
+      <c r="T2" s="92" t="s">
         <v>30</v>
       </c>
       <c r="U2" s="66"/>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="69.75" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="100" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="85">
+      <c r="G3" s="83">
         <v>0</v>
       </c>
-      <c r="H3" s="78">
+      <c r="H3" s="77">
         <v>0.375</v>
       </c>
-      <c r="I3" s="79" t="s">
+      <c r="I3" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="80"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="108" t="s">
+      <c r="J3" s="79"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="101"/>
-      <c r="N3" s="109" t="s">
+      <c r="M3" s="92"/>
+      <c r="N3" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
       <c r="S3" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="101"/>
+      <c r="T3" s="92"/>
       <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:21" s="5" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="77" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="78" t="s">
+      <c r="F4" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="78">
+      <c r="G4" s="77">
         <v>0</v>
       </c>
-      <c r="H4" s="78">
+      <c r="H4" s="77">
         <v>1.5</v>
       </c>
-      <c r="I4" s="86"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="78"/>
-      <c r="L4" s="108" t="s">
+      <c r="I4" s="84"/>
+      <c r="J4" s="79"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="101"/>
-      <c r="N4" s="109" t="s">
+      <c r="M4" s="92"/>
+      <c r="N4" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="101"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="92"/>
       <c r="S4" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="T4" s="101"/>
+      <c r="T4" s="92"/>
       <c r="U4" s="66"/>
     </row>
     <row r="5" spans="1:21" s="5" customFormat="1" ht="137.25">
-      <c r="A5" s="81"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="87" t="s">
+      <c r="A5" s="80"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="145"/>
+      <c r="E5" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="88">
+      <c r="G5" s="86">
         <v>0</v>
       </c>
-      <c r="H5" s="89">
+      <c r="H5" s="87">
         <v>20000</v>
       </c>
-      <c r="I5" s="90" t="s">
+      <c r="I5" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="80"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="108" t="s">
+      <c r="J5" s="79"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="101"/>
-      <c r="N5" s="109" t="s">
+      <c r="M5" s="92"/>
+      <c r="N5" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="O5" s="101"/>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="101"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="92"/>
+      <c r="R5" s="92"/>
       <c r="S5" s="66"/>
-      <c r="T5" s="101"/>
+      <c r="T5" s="92"/>
       <c r="U5" s="66"/>
     </row>
     <row r="6" spans="1:21" s="5" customFormat="1" ht="45.75">
-      <c r="A6" s="91"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="110" t="s">
+      <c r="A6" s="80"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="95" t="s">
+      <c r="F6" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="103">
         <v>0</v>
       </c>
-      <c r="H6" s="96">
+      <c r="H6" s="104">
         <v>146167</v>
       </c>
-      <c r="I6" s="90" t="s">
+      <c r="I6" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="80"/>
-      <c r="K6" s="78"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="107"/>
       <c r="L6" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="101"/>
-      <c r="N6" s="109" t="s">
+      <c r="M6" s="109"/>
+      <c r="N6" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="101"/>
-      <c r="P6" s="101"/>
-      <c r="Q6" s="101"/>
-      <c r="R6" s="101"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="101"/>
-      <c r="U6" s="66"/>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="67"/>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="11"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="111"/>
+      <c r="T6" s="109"/>
+      <c r="U6" s="111"/>
+    </row>
+    <row r="7" spans="1:21" ht="54" customHeight="1">
+      <c r="A7" s="124">
+        <v>126602</v>
+      </c>
+      <c r="B7" s="122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="146">
+        <v>508296</v>
+      </c>
+      <c r="E7" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="84">
+        <v>0</v>
+      </c>
+      <c r="H7" s="84">
+        <v>0.254</v>
+      </c>
+      <c r="I7" s="128" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="117" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="130">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="117" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="119"/>
+      <c r="N7" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="117" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="119"/>
+      <c r="R7" s="119" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="117" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="117" t="s">
+        <v>30</v>
+      </c>
+      <c r="U7" s="101"/>
+    </row>
+    <row r="8" spans="1:21" ht="52.5" customHeight="1">
+      <c r="A8" s="125"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="113" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="105" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="114">
+        <v>0</v>
+      </c>
+      <c r="H8" s="114">
+        <v>2133</v>
+      </c>
+      <c r="I8" s="129"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="132"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="118"/>
+      <c r="T8" s="118"/>
+      <c r="U8" s="115"/>
+    </row>
+    <row r="9" spans="1:21" ht="58.5" customHeight="1">
+      <c r="A9" s="124">
+        <v>133343</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="133" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="148">
+        <v>1770000</v>
+      </c>
+      <c r="E9" s="84" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="84">
+        <v>0</v>
+      </c>
+      <c r="H9" s="116">
+        <v>100000</v>
+      </c>
+      <c r="I9" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="117" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="130">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="117" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="117"/>
+      <c r="N9" s="121" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="117" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117" t="s">
+        <v>28</v>
+      </c>
+      <c r="S9" s="121" t="s">
+        <v>53</v>
+      </c>
+      <c r="T9" s="117"/>
+      <c r="U9" s="117"/>
     </row>
     <row r="10" spans="1:21" ht="26.25" customHeight="1">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="124"/>
+      <c r="C10" s="134"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84">
+        <v>0.02</v>
+      </c>
+      <c r="I10" s="128"/>
+      <c r="J10" s="117"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="117"/>
+      <c r="S10" s="121"/>
+      <c r="T10" s="117"/>
+      <c r="U10" s="117"/>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="10"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
+      <c r="C11" s="112" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="149"/>
       <c r="E11" s="67"/>
       <c r="F11" s="67"/>
       <c r="G11" s="67"/>
@@ -1615,7 +1893,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
+      <c r="D12" s="149"/>
       <c r="E12" s="67"/>
       <c r="F12" s="67"/>
       <c r="G12" s="67"/>
@@ -1626,18 +1904,21 @@
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="11"/>
-      <c r="D13" s="12"/>
+      <c r="D13" s="149"/>
       <c r="E13" s="67"/>
       <c r="F13" s="67"/>
       <c r="G13" s="67"/>
       <c r="H13" s="67"/>
       <c r="I13" s="67"/>
+      <c r="M13" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
-      <c r="D14" s="12"/>
+      <c r="D14" s="149"/>
       <c r="E14" s="67"/>
       <c r="F14" s="67"/>
       <c r="G14" s="67"/>
@@ -1645,6 +1926,41 @@
       <c r="I14" s="67"/>
     </row>
   </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="P7:P8"/>
+  </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6" xr:uid="{FBE3BB32-5375-454C-95CF-ACD4944FDEA9}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
@@ -1652,10 +1968,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P6" xr:uid="{E2973C99-4CCD-48B6-A4B2-BD4397205CF7}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N6" xr:uid="{E67BA2D6-35D5-455A-A6F9-1F441360B09A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N7 N9" xr:uid="{E67BA2D6-35D5-455A-A6F9-1F441360B09A}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O6" xr:uid="{F88D5E25-1518-4B85-8969-BBA9D1D913CD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O7 O9" xr:uid="{F88D5E25-1518-4B85-8969-BBA9D1D913CD}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L6" xr:uid="{767CBA24-2B16-4B7B-8825-CFE8AB5915FB}">
@@ -1676,6 +1992,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{83F1A697-A541-4B9C-8D8B-4F40E2A5EAF0}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{DB46CF99-3439-405C-B764-D3675929158E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -1686,13 +2003,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E7:E14</xm:sqref>
+          <xm:sqref>E7 E9:E14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C4E58264-8C52-4FCE-85E9-3E7F59D6FBED}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E6</xm:sqref>
+          <xm:sqref>E2:E6 E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1759,10 +2076,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="M1" s="55" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="N1" s="69"/>
       <c r="O1" s="70" t="s">
@@ -1799,16 +2116,16 @@
       <c r="AJ1" s="69"/>
     </row>
     <row r="2" spans="1:36" s="51" customFormat="1" ht="60" customHeight="1">
-      <c r="A2" s="116" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="117" t="s">
+      <c r="A2" s="140" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="118" t="s">
+      <c r="C2" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="116">
+      <c r="D2" s="140">
         <v>4000000</v>
       </c>
       <c r="E2" s="56" t="s">
@@ -1824,11 +2141,11 @@
       <c r="I2" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="111" t="s">
+      <c r="J2" s="135" t="s">
         <v>25</v>
       </c>
       <c r="K2" s="59"/>
-      <c r="L2" s="111" t="s">
+      <c r="L2" s="135" t="s">
         <v>26</v>
       </c>
       <c r="M2" s="59"/>
@@ -1841,7 +2158,7 @@
       </c>
       <c r="Q2" s="66"/>
       <c r="R2" s="66" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="S2" s="66" t="s">
         <v>28</v>
@@ -1865,10 +2182,10 @@
       <c r="AJ2" s="66"/>
     </row>
     <row r="3" spans="1:36" s="51" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="116"/>
+      <c r="A3" s="140"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="140"/>
       <c r="E3" s="56" t="s">
         <v>31</v>
       </c>
@@ -1879,14 +2196,14 @@
         <v>0</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I3" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="111"/>
+      <c r="J3" s="135"/>
       <c r="K3" s="59"/>
-      <c r="L3" s="111"/>
+      <c r="L3" s="135"/>
       <c r="M3" s="59"/>
       <c r="N3" s="66"/>
       <c r="O3" s="66" t="s">
@@ -1917,10 +2234,10 @@
       <c r="AJ3" s="66"/>
     </row>
     <row r="4" spans="1:36" s="51" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A4" s="116"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="116"/>
+      <c r="A4" s="140"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="140"/>
       <c r="E4" s="56" t="s">
         <v>31</v>
       </c>
@@ -1934,9 +2251,9 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="61"/>
-      <c r="J4" s="111"/>
+      <c r="J4" s="135"/>
       <c r="K4" s="59"/>
-      <c r="L4" s="111"/>
+      <c r="L4" s="135"/>
       <c r="M4" s="62"/>
       <c r="N4" s="66"/>
       <c r="O4" s="66" t="s">
@@ -1967,12 +2284,12 @@
       <c r="AJ4" s="66"/>
     </row>
     <row r="5" spans="1:36" s="51" customFormat="1" ht="39" customHeight="1">
-      <c r="A5" s="116"/>
-      <c r="B5" s="117"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="116"/>
+      <c r="A5" s="140"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="140"/>
       <c r="E5" s="63" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F5" s="64" t="s">
         <v>37</v>
@@ -1986,9 +2303,9 @@
       <c r="I5" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="111"/>
+      <c r="J5" s="135"/>
       <c r="K5" s="59"/>
-      <c r="L5" s="111"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="62"/>
       <c r="N5" s="66"/>
       <c r="O5" s="66" t="s">
@@ -2019,12 +2336,12 @@
       <c r="AJ5" s="66"/>
     </row>
     <row r="6" spans="1:36" s="51" customFormat="1" ht="33.75" customHeight="1">
-      <c r="A6" s="116"/>
-      <c r="B6" s="117"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="116"/>
+      <c r="A6" s="140"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="142"/>
+      <c r="D6" s="140"/>
       <c r="E6" s="64" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F6" s="63" t="s">
         <v>40</v>
@@ -2038,9 +2355,9 @@
       <c r="I6" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="111"/>
+      <c r="J6" s="135"/>
       <c r="K6" s="59"/>
-      <c r="L6" s="111"/>
+      <c r="L6" s="135"/>
       <c r="M6" s="62"/>
       <c r="N6" s="66"/>
       <c r="O6" s="66" t="s">
@@ -2169,62 +2486,62 @@
       <c r="H15" s="18"/>
     </row>
     <row r="16" spans="1:36">
-      <c r="A16" s="112"/>
-      <c r="B16" s="113"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="115"/>
+      <c r="A16" s="136"/>
+      <c r="B16" s="137"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139"/>
       <c r="F16" s="14"/>
       <c r="G16" s="13"/>
       <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="112"/>
-      <c r="B17" s="113"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="115"/>
+      <c r="A17" s="136"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="139"/>
       <c r="F17" s="14"/>
       <c r="G17" s="13"/>
       <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="112"/>
-      <c r="B18" s="113"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="115"/>
+      <c r="A18" s="136"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="139"/>
       <c r="G18" s="22"/>
       <c r="I18" s="16"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="112"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="115"/>
+      <c r="A19" s="136"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="139"/>
       <c r="G19" s="13"/>
       <c r="H19"/>
       <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="112"/>
-      <c r="B20" s="113"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="115"/>
+      <c r="A20" s="136"/>
+      <c r="B20" s="137"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="139"/>
       <c r="F20" s="21"/>
       <c r="G20" s="22"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="112"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="115"/>
+      <c r="A21" s="136"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="139"/>
       <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="112"/>
-      <c r="B22" s="113"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="115"/>
+      <c r="A22" s="136"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="139"/>
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:9">
@@ -2414,7 +2731,7 @@
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="60">
       <c r="A3" s="9" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B3" s="40" t="s">
         <v>21</v>
@@ -2423,7 +2740,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E3" s="43" t="s">
         <v>19</v>
@@ -2435,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="45" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I3" s="45" t="s">
         <v>24</v>
@@ -2456,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I4" s="46" t="s">
         <v>33</v>
@@ -2477,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I5" s="48"/>
     </row>
@@ -2487,7 +2804,7 @@
       <c r="C6" s="11"/>
       <c r="D6" s="12"/>
       <c r="E6" s="49" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>37</v>
@@ -2496,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I6" s="49" t="s">
         <v>38</v>
@@ -2511,13 +2828,13 @@
         <v>31</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G7" s="48">
         <v>0</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I7" s="49" t="s">
         <v>41</v>
@@ -2633,62 +2950,62 @@
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="112"/>
-      <c r="B18" s="113"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="115"/>
+      <c r="A18" s="136"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="139"/>
       <c r="F18" s="14"/>
       <c r="G18" s="13"/>
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="112"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114"/>
-      <c r="D19" s="115"/>
+      <c r="A19" s="136"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="139"/>
       <c r="F19" s="14"/>
       <c r="G19" s="13"/>
       <c r="H19" s="15"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="112"/>
-      <c r="B20" s="113"/>
-      <c r="C20" s="114"/>
-      <c r="D20" s="115"/>
+      <c r="A20" s="136"/>
+      <c r="B20" s="137"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="139"/>
       <c r="G20" s="22"/>
       <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="112"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="115"/>
+      <c r="A21" s="136"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="139"/>
       <c r="G21" s="13"/>
       <c r="H21"/>
       <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="112"/>
-      <c r="B22" s="113"/>
-      <c r="C22" s="114"/>
-      <c r="D22" s="115"/>
+      <c r="A22" s="136"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="139"/>
       <c r="F22" s="21"/>
       <c r="G22" s="22"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="112"/>
-      <c r="B23" s="113"/>
-      <c r="C23" s="114"/>
-      <c r="D23" s="115"/>
+      <c r="A23" s="136"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="139"/>
       <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="112"/>
-      <c r="B24" s="113"/>
-      <c r="C24" s="114"/>
-      <c r="D24" s="115"/>
+      <c r="A24" s="136"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="139"/>
       <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:9">
@@ -2806,179 +3123,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="93" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="119" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="103" t="s">
-        <v>58</v>
+      <c r="A2" s="151" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="94" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="103" t="s">
-        <v>59</v>
+      <c r="B3" s="94" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="119" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="103" t="s">
-        <v>61</v>
+      <c r="A4" s="151" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="94" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="151" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="94" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45.75">
+      <c r="A6" s="151" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="94" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="151" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="94" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30.75">
+      <c r="A8" s="151" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="94" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30.75">
+      <c r="A9" s="151" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="151" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="152" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="151" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="152" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30.75">
+      <c r="A12" s="151" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="94" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="151" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="103" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45.75">
-      <c r="A6" s="119" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="119" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="103" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="119" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="103" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="119" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="103" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="119" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="120" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="119" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="120" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="119" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="103" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="119" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="120" t="s">
-        <v>78</v>
+      <c r="B13" s="152" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="119" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="120" t="s">
-        <v>80</v>
+      <c r="A14" s="151" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="152" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="119" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="120" t="s">
-        <v>82</v>
+      <c r="A15" s="151" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="152" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="119" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="120" t="s">
-        <v>84</v>
+      <c r="A16" s="151" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="152" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="151" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="103" t="s">
-        <v>85</v>
+      <c r="B17" s="94" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="119" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="120" t="s">
-        <v>87</v>
+      <c r="A18" s="151" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="152" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="119" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="120" t="s">
-        <v>89</v>
+      <c r="A19" s="151" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="152" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="119" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="120" t="s">
-        <v>91</v>
+      <c r="A20" s="151" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="152" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="119" t="s">
+      <c r="A21" s="151" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="121" t="s">
-        <v>92</v>
+      <c r="B21" s="153" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="119" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="120" t="s">
-        <v>94</v>
+      <c r="A22" s="151" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="152" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2987,6 +3304,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2995,7 +3323,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3250,25 +3578,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BBFE1BD-9BE7-450B-B956-AF3B3ABCBDB9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Iran - Energy Projects.xlsx
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -747,22 +747,16 @@
     <xf numFmtId="165" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1132,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="15.7109375" customWidth="1" style="2" min="1" max="1"/>
@@ -1649,29 +1643,22 @@
       <c r="X7" s="117" t="n"/>
     </row>
     <row r="8" ht="52.5" customHeight="1">
-      <c r="A8" s="156" t="n"/>
-      <c r="B8" s="156" t="n"/>
-      <c r="C8" s="156" t="n"/>
-      <c r="D8" s="156" t="n"/>
-      <c r="E8" s="156" t="n"/>
-      <c r="F8" s="156" t="n"/>
-      <c r="G8" s="156" t="n"/>
-      <c r="H8" s="156" t="n"/>
-      <c r="I8" s="156" t="n"/>
-      <c r="J8" s="156" t="n"/>
-      <c r="K8" s="156" t="n"/>
-      <c r="L8" s="156" t="n"/>
-      <c r="M8" s="156" t="n"/>
-      <c r="N8" s="156" t="n"/>
-      <c r="O8" s="156" t="n"/>
-      <c r="P8" s="157" t="n"/>
-      <c r="Q8" s="156" t="n"/>
-      <c r="R8" s="156" t="n"/>
-      <c r="S8" s="157" t="n"/>
-      <c r="T8" s="157" t="n"/>
-      <c r="U8" s="157" t="n"/>
-      <c r="V8" s="156" t="n"/>
-      <c r="W8" s="156" t="n"/>
+      <c r="I8" s="113" t="inlineStr">
+        <is>
+          <t>GHG Emissions Reduction</t>
+        </is>
+      </c>
+      <c r="J8" s="105" t="inlineStr">
+        <is>
+          <t>tCO2 saved</t>
+        </is>
+      </c>
+      <c r="K8" s="129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="129" t="n">
+        <v>2133</v>
+      </c>
       <c r="X8" s="118" t="n"/>
     </row>
     <row r="9" ht="58.5" customHeight="1">
@@ -1683,7 +1670,7 @@
           <t>Water Stress in Chabahar</t>
         </is>
       </c>
-      <c r="C9" s="158" t="inlineStr">
+      <c r="C9" s="156" t="inlineStr">
         <is>
           <t>https://open.undp.org/projects/00146138</t>
         </is>
@@ -1691,9 +1678,9 @@
       <c r="D9" s="148" t="n">
         <v>1770000</v>
       </c>
-      <c r="E9" s="159" t="n"/>
-      <c r="F9" s="159" t="n"/>
-      <c r="G9" s="159" t="n"/>
+      <c r="E9" s="157" t="n"/>
+      <c r="F9" s="157" t="n"/>
+      <c r="G9" s="157" t="n"/>
       <c r="H9" s="148" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -1755,14 +1742,6 @@
       <c r="X9" s="117" t="n"/>
     </row>
     <row r="10" ht="26.25" customHeight="1">
-      <c r="A10" s="124" t="n"/>
-      <c r="B10" s="124" t="n"/>
-      <c r="C10" s="158" t="n"/>
-      <c r="D10" s="148" t="n"/>
-      <c r="E10" s="159" t="n"/>
-      <c r="F10" s="159" t="n"/>
-      <c r="G10" s="159" t="n"/>
-      <c r="H10" s="148" t="n"/>
       <c r="I10" s="128" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -1770,90 +1749,52 @@
       </c>
       <c r="J10" s="128" t="inlineStr">
         <is>
-          <t>Installed capacity in MW for access/productive-use outputs</t>
-        </is>
-      </c>
-      <c r="K10" s="128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="161" t="n"/>
-      <c r="M10" s="162" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N10" s="117" t="n"/>
-      <c r="O10" s="130" t="n"/>
-      <c r="P10" s="117" t="n"/>
-      <c r="Q10" s="121" t="n"/>
-      <c r="R10" s="117" t="n"/>
-      <c r="S10" s="117" t="n"/>
-      <c r="T10" s="117" t="n"/>
-      <c r="U10" s="117" t="n"/>
-      <c r="V10" s="121" t="n"/>
-      <c r="W10" s="117" t="n"/>
-      <c r="X10" s="117" t="n"/>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="K10" s="128" t="n"/>
+      <c r="L10" s="128" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="156" t="n"/>
-      <c r="B11" s="156" t="n"/>
-      <c r="C11" s="156" t="n"/>
-      <c r="D11" s="156" t="n"/>
-      <c r="E11" s="159" t="n"/>
-      <c r="F11" s="159" t="n"/>
-      <c r="G11" s="159" t="n"/>
-      <c r="H11" s="148" t="n"/>
-      <c r="I11" s="156" t="n"/>
-      <c r="J11" s="156" t="n"/>
-      <c r="K11" s="156" t="n"/>
-      <c r="L11" s="156" t="n"/>
-      <c r="M11" s="156" t="n"/>
-      <c r="N11" s="156" t="n"/>
-      <c r="O11" s="156" t="n"/>
-      <c r="P11" s="156" t="n"/>
-      <c r="Q11" s="156" t="n"/>
-      <c r="R11" s="156" t="n"/>
-      <c r="S11" s="156" t="n"/>
-      <c r="T11" s="156" t="n"/>
-      <c r="U11" s="156" t="n"/>
-      <c r="V11" s="121" t="n"/>
-      <c r="W11" s="117" t="n"/>
-      <c r="X11" s="117" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="112" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D11" s="149" t="n"/>
+      <c r="E11" s="149" t="n"/>
+      <c r="F11" s="149" t="n"/>
+      <c r="G11" s="149" t="n"/>
+      <c r="H11" s="149" t="n"/>
+      <c r="I11" s="67" t="n"/>
+      <c r="J11" s="67" t="n"/>
+      <c r="K11" s="67" t="n"/>
+      <c r="L11" s="67" t="n"/>
+      <c r="M11" s="67" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="156" t="n"/>
-      <c r="B12" s="156" t="n"/>
-      <c r="C12" s="156" t="n"/>
-      <c r="D12" s="156" t="n"/>
-      <c r="E12" s="156" t="n"/>
-      <c r="F12" s="156" t="n"/>
-      <c r="G12" s="156" t="n"/>
-      <c r="H12" s="156" t="n"/>
-      <c r="I12" s="156" t="n"/>
-      <c r="J12" s="156" t="n"/>
-      <c r="K12" s="156" t="n"/>
-      <c r="L12" s="156" t="n"/>
-      <c r="M12" s="156" t="n"/>
-      <c r="N12" s="156" t="n"/>
-      <c r="O12" s="156" t="n"/>
-      <c r="P12" s="156" t="n"/>
-      <c r="Q12" s="156" t="n"/>
-      <c r="R12" s="156" t="n"/>
-      <c r="S12" s="156" t="n"/>
-      <c r="T12" s="156" t="n"/>
-      <c r="U12" s="156" t="n"/>
-      <c r="V12" s="156" t="n"/>
-      <c r="W12" s="156" t="n"/>
-      <c r="X12" s="156" t="n"/>
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="149" t="n"/>
+      <c r="E12" s="149" t="n"/>
+      <c r="F12" s="149" t="n"/>
+      <c r="G12" s="149" t="n"/>
+      <c r="H12" s="149" t="n"/>
+      <c r="I12" s="67" t="n"/>
+      <c r="J12" s="67" t="n"/>
+      <c r="K12" s="67" t="n"/>
+      <c r="L12" s="67" t="n"/>
+      <c r="M12" s="67" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="10" t="n"/>
-      <c r="C13" s="112" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="C13" s="11" t="n"/>
       <c r="D13" s="149" t="n"/>
       <c r="E13" s="149" t="n"/>
       <c r="F13" s="149" t="n"/>
@@ -1864,6 +1805,11 @@
       <c r="K13" s="67" t="n"/>
       <c r="L13" s="67" t="n"/>
       <c r="M13" s="67" t="n"/>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n"/>
@@ -1880,78 +1826,8 @@
       <c r="L14" s="67" t="n"/>
       <c r="M14" s="67" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="149" t="n"/>
-      <c r="E15" s="149" t="n"/>
-      <c r="F15" s="149" t="n"/>
-      <c r="G15" s="149" t="n"/>
-      <c r="H15" s="149" t="n"/>
-      <c r="I15" s="67" t="n"/>
-      <c r="J15" s="67" t="n"/>
-      <c r="K15" s="67" t="n"/>
-      <c r="L15" s="67" t="n"/>
-      <c r="M15" s="67" t="n"/>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="149" t="n"/>
-      <c r="E16" s="149" t="n"/>
-      <c r="F16" s="149" t="n"/>
-      <c r="G16" s="149" t="n"/>
-      <c r="H16" s="149" t="n"/>
-      <c r="I16" s="67" t="n"/>
-      <c r="J16" s="67" t="n"/>
-      <c r="K16" s="67" t="n"/>
-      <c r="L16" s="67" t="n"/>
-      <c r="M16" s="67" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="N7:N8"/>
-  </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1978,12 +1854,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -2232,10 +2102,10 @@
       <c r="AJ2" s="66" t="n"/>
     </row>
     <row r="3" ht="36.75" customFormat="1" customHeight="1" s="51">
-      <c r="A3" s="157" t="n"/>
-      <c r="B3" s="157" t="n"/>
-      <c r="C3" s="157" t="n"/>
-      <c r="D3" s="157" t="n"/>
+      <c r="A3" s="158" t="n"/>
+      <c r="B3" s="158" t="n"/>
+      <c r="C3" s="158" t="n"/>
+      <c r="D3" s="158" t="n"/>
       <c r="E3" s="56" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2262,9 +2132,9 @@
 </t>
         </is>
       </c>
-      <c r="J3" s="157" t="n"/>
+      <c r="J3" s="158" t="n"/>
       <c r="K3" s="59" t="n"/>
-      <c r="L3" s="157" t="n"/>
+      <c r="L3" s="158" t="n"/>
       <c r="M3" s="59" t="n"/>
       <c r="N3" s="66" t="n"/>
       <c r="O3" s="66" t="inlineStr">
@@ -2299,10 +2169,10 @@
       <c r="AJ3" s="66" t="n"/>
     </row>
     <row r="4" ht="40.5" customFormat="1" customHeight="1" s="51">
-      <c r="A4" s="157" t="n"/>
-      <c r="B4" s="157" t="n"/>
-      <c r="C4" s="157" t="n"/>
-      <c r="D4" s="157" t="n"/>
+      <c r="A4" s="158" t="n"/>
+      <c r="B4" s="158" t="n"/>
+      <c r="C4" s="158" t="n"/>
+      <c r="D4" s="158" t="n"/>
       <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
@@ -2320,9 +2190,9 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="61" t="n"/>
-      <c r="J4" s="157" t="n"/>
+      <c r="J4" s="158" t="n"/>
       <c r="K4" s="59" t="n"/>
-      <c r="L4" s="157" t="n"/>
+      <c r="L4" s="158" t="n"/>
       <c r="M4" s="62" t="n"/>
       <c r="N4" s="66" t="n"/>
       <c r="O4" s="66" t="inlineStr">
@@ -2357,10 +2227,10 @@
       <c r="AJ4" s="66" t="n"/>
     </row>
     <row r="5" ht="39" customFormat="1" customHeight="1" s="51">
-      <c r="A5" s="157" t="n"/>
-      <c r="B5" s="157" t="n"/>
-      <c r="C5" s="157" t="n"/>
-      <c r="D5" s="157" t="n"/>
+      <c r="A5" s="158" t="n"/>
+      <c r="B5" s="158" t="n"/>
+      <c r="C5" s="158" t="n"/>
+      <c r="D5" s="158" t="n"/>
       <c r="E5" s="63" t="inlineStr">
         <is>
           <t>Capacity Training</t>
@@ -2388,9 +2258,9 @@
 of ministry of power ( MoP</t>
         </is>
       </c>
-      <c r="J5" s="157" t="n"/>
+      <c r="J5" s="158" t="n"/>
       <c r="K5" s="59" t="n"/>
-      <c r="L5" s="157" t="n"/>
+      <c r="L5" s="158" t="n"/>
       <c r="M5" s="62" t="n"/>
       <c r="N5" s="66" t="n"/>
       <c r="O5" s="66" t="inlineStr">
@@ -2425,10 +2295,10 @@
       <c r="AJ5" s="66" t="n"/>
     </row>
     <row r="6" ht="33.75" customFormat="1" customHeight="1" s="51">
-      <c r="A6" s="156" t="n"/>
-      <c r="B6" s="156" t="n"/>
-      <c r="C6" s="156" t="n"/>
-      <c r="D6" s="156" t="n"/>
+      <c r="A6" s="159" t="n"/>
+      <c r="B6" s="159" t="n"/>
+      <c r="C6" s="159" t="n"/>
+      <c r="D6" s="159" t="n"/>
       <c r="E6" s="64" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
@@ -2451,9 +2321,9 @@
 municipality and 6 other buildings)</t>
         </is>
       </c>
-      <c r="J6" s="156" t="n"/>
+      <c r="J6" s="159" t="n"/>
       <c r="K6" s="59" t="n"/>
-      <c r="L6" s="156" t="n"/>
+      <c r="L6" s="159" t="n"/>
       <c r="M6" s="62" t="n"/>
       <c r="N6" s="66" t="n"/>
       <c r="O6" s="66" t="inlineStr">
